--- a/hrm/.plans/elearning-quan-ly/bao-cao-hoc-vien-ngoai/testcase.xlsx
+++ b/hrm/.plans/elearning-quan-ly/bao-cao-hoc-vien-ngoai/testcase.xlsx
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -802,7 +802,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Nút 'Xuất Excel' hiện chỉ là demo (toast 'Xuất Excel (demo)', chưa tải file). Nút 'In báo cáo' in bảng hiện tại. Thẻ KPI + bảng tính lại theo bộ lọc.</t>
+          <t>Nút 'Xuất Excel' tải file thật (bao-cao-hoc-vien-ngoai-YYYYMMDD-HHmm.xlsx) gồm tiêu đề + dòng KPI + bảng theo bộ lọc hiện tại. Nút 'In báo cáo' in bảng hiện tại. Thẻ KPI + bảng tính lại theo bộ lọc.</t>
         </is>
       </c>
       <c r="C10" s="4" t="n"/>
@@ -2044,7 +2044,7 @@
       <c r="N35" s="4" t="n"/>
       <c r="O35" s="5" t="n"/>
     </row>
-    <row r="36" ht="30" customHeight="1">
+    <row r="36" ht="114" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
           <t>Báo cáo HV ngoài</t>
@@ -2062,17 +2062,17 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Xuất Excel (demo)</t>
+          <t>Xuất Excel theo bộ lọc</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Đang xem báo cáo</t>
+          <t>Đang xem báo cáo có dữ liệu (đã lọc)</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -2087,12 +2087,14 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>- Hiện toast 'Xuất Excel (demo)' (chưa tải file thật — ghi nhận chức năng chưa hoàn thiện)</t>
+          <t>- Nút hiện 'Đang xuất...'; tải file bao-cao-hoc-vien-ngoai-YYYYMMDD-HHmm.xlsx
+- File gồm: tiêu đề 'DANH SÁCH HỌC VIÊN NGOÀI — THỐNG KÊ HỌC TẬP', dòng KPI (Học viên/Đăng ký/Đang học/Hoàn thành/Đạt), bảng cột STT/Họ tên/Email/Công ty/Nguồn đăng ký/Ngày tham gia/Đăng ký/Đang học/Hoàn thành/Đã đạt/Tỷ lệ HT (%)
+- Toast 'Đã xuất Excel thành công'</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>Xuất Excel đang demo</t>
+          <t>Xuất theo tableData hiện tại</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr"/>
@@ -2126,12 +2128,12 @@
       </c>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>TC_04.002</t>
+          <t>TC_04.003</t>
         </is>
       </c>
       <c r="D37" s="14" t="inlineStr">
         <is>
-          <t>In báo cáo</t>
+          <t>Xuất Excel khi không có dữ liệu</t>
         </is>
       </c>
       <c r="E37" s="15" t="inlineStr">
@@ -2141,12 +2143,12 @@
       </c>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>Đang xem báo cáo</t>
+          <t>Bộ lọc không ra kết quả (bảng rỗng)</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>1. Bấm 'In báo cáo'</t>
+          <t>1. Bấm 'Xuất Excel'</t>
         </is>
       </c>
       <c r="H37" s="14" t="inlineStr">
@@ -2156,12 +2158,12 @@
       </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
-          <t>- Mở chế độ in bảng hiện tại</t>
+          <t>- Toast 'Không có dữ liệu để xuất', không tải file</t>
         </is>
       </c>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Chặn xuất khi rỗng</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr"/>
@@ -2182,109 +2184,178 @@
       </c>
       <c r="O37" s="14" t="inlineStr"/>
     </row>
-    <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="11" t="n"/>
-      <c r="B38" s="11" t="n"/>
-      <c r="C38" s="12" t="inlineStr">
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Báo cáo HV ngoài</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>XUẤT EXCEL / IN</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>TC_04.002</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>In báo cáo</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Đang xem báo cáo</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>1. Bấm 'In báo cáo'</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>- Mở chế độ in bảng hiện tại</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="11" t="n"/>
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="12" t="inlineStr">
         <is>
           <t>V. LUỒNG XUYÊN SUỐT (E2E)</t>
         </is>
       </c>
-      <c r="D38" s="4" t="n"/>
-      <c r="E38" s="4" t="n"/>
-      <c r="F38" s="4" t="n"/>
-      <c r="G38" s="4" t="n"/>
-      <c r="H38" s="4" t="n"/>
-      <c r="I38" s="4" t="n"/>
-      <c r="J38" s="4" t="n"/>
-      <c r="K38" s="4" t="n"/>
-      <c r="L38" s="4" t="n"/>
-      <c r="M38" s="4" t="n"/>
-      <c r="N38" s="4" t="n"/>
-      <c r="O38" s="5" t="n"/>
-    </row>
-    <row r="39" ht="34" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="n"/>
+      <c r="J39" s="4" t="n"/>
+      <c r="K39" s="4" t="n"/>
+      <c r="L39" s="4" t="n"/>
+      <c r="M39" s="4" t="n"/>
+      <c r="N39" s="4" t="n"/>
+      <c r="O39" s="5" t="n"/>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t>Báo cáo HV ngoài</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t>LUỒNG XUYÊN SUỐT (E2E)</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C40" s="14" t="inlineStr">
         <is>
           <t>TC_05.001</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D40" s="14" t="inlineStr">
         <is>
           <t>Lọc → xem KPI → chi tiết</t>
         </is>
       </c>
-      <c r="E39" s="13" t="inlineStr">
+      <c r="E40" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F40" s="14" t="inlineStr">
         <is>
           <t>Có ≥5 học viên có ghi danh</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G40" s="14" t="inlineStr">
         <is>
           <t>1. 'Trạng thái học' = Có đăng ký khoá
 2. Đọc KPI
 3. Click 1 học viên xem chi tiết</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
+      <c r="H40" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
         <is>
           <t>- B1: bảng chỉ học viên có đăng ký
 - B2: KPI khớp tổng bảng
 - B3: popup chi tiết khóa/lộ trình học viên</t>
         </is>
       </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr"/>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="inlineStr"/>
+      <c r="J40" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K40" s="14" t="inlineStr"/>
+      <c r="L40" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="M40" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="N40" s="14" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="O40" s="14" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="27">
     <mergeCell ref="B4:O4"/>
     <mergeCell ref="C23:O23"/>
+    <mergeCell ref="C39:O39"/>
     <mergeCell ref="B7:O7"/>
     <mergeCell ref="B3:O3"/>
     <mergeCell ref="I12:K12"/>
     <mergeCell ref="L11:O11"/>
-    <mergeCell ref="C38:O38"/>
     <mergeCell ref="I14:K14"/>
     <mergeCell ref="B2:O2"/>
     <mergeCell ref="C18:O18"/>
@@ -2307,7 +2378,7 @@
     <mergeCell ref="B5:O5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="L18:N140" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L18:N141" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Passed,Failed,Pending,Not Executed"</formula1>
     </dataValidation>
   </dataValidations>
